--- a/tame_output/ON/bt/strategyON_20231221.xlsx
+++ b/tame_output/ON/bt/strategyON_20231221.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>472.3%</t>
+          <t>465.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-160.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-113.0%</t>
+          <t>-112.8%</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,11 +1107,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-19.1%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.1%</t>
+          <t>-130.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-35.7%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.9%</t>
+          <t>112.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1413,11 +1413,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>4.6%</t>
         </is>
       </c>
     </row>
@@ -42387,16 +42387,16 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-3.221769263852956</v>
+        <v>-3.279498522578539</v>
       </c>
       <c r="E1777" t="n">
-        <v>1.795252531356702</v>
+        <v>1.772160827866469</v>
       </c>
       <c r="F1777" t="n">
-        <v>0.2563152514922422</v>
+        <v>0.1985859927666589</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.238105812106978</v>
+        <v>3.203468256871628</v>
       </c>
     </row>
     <row r="1778">
@@ -42410,16 +42410,16 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-3.211949545692405</v>
+        <v>-3.269678804417988</v>
       </c>
       <c r="E1778" t="n">
-        <v>1.796649130108152</v>
+        <v>1.773557426617919</v>
       </c>
       <c r="F1778" t="n">
-        <v>0.2627451917089296</v>
+        <v>0.2050159329833464</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.23943248772422</v>
+        <v>3.20479493248887</v>
       </c>
     </row>
     <row r="1779">
@@ -42433,16 +42433,16 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-3.210147918853451</v>
+        <v>-3.267877177579034</v>
       </c>
       <c r="E1779" t="n">
-        <v>1.782618342847359</v>
+        <v>1.759526639357126</v>
       </c>
       <c r="F1779" t="n">
-        <v>0.2627451917089296</v>
+        <v>0.2050159329833464</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.224681049727846</v>
+        <v>3.190043494492496</v>
       </c>
     </row>
     <row r="1780">
@@ -42456,16 +42456,16 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-3.209159237109283</v>
+        <v>-3.266888495834866</v>
       </c>
       <c r="E1780" t="n">
-        <v>1.781127571860698</v>
+        <v>1.758035868370465</v>
       </c>
       <c r="F1780" t="n">
-        <v>0.2627451917089296</v>
+        <v>0.2050159329833464</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.222794806043518</v>
+        <v>3.188157250808168</v>
       </c>
     </row>
     <row r="1781">
@@ -42479,16 +42479,16 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-3.201162882587745</v>
+        <v>-3.258892141313328</v>
       </c>
       <c r="E1781" t="n">
-        <v>1.786299740125154</v>
+        <v>1.763208036634921</v>
       </c>
       <c r="F1781" t="n">
-        <v>0.2707415462304682</v>
+        <v>0.2130122875048849</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.229566245212281</v>
+        <v>3.194928689976932</v>
       </c>
     </row>
     <row r="1782">
@@ -42502,16 +42502,16 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-3.196179131915836</v>
+        <v>-3.253908390641419</v>
       </c>
       <c r="E1782" t="n">
-        <v>1.800131820984829</v>
+        <v>1.777040117494596</v>
       </c>
       <c r="F1782" t="n">
-        <v>0.2757252969023769</v>
+        <v>0.2179960381767936</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.244395076206338</v>
+        <v>3.209757520970988</v>
       </c>
     </row>
     <row r="1783">
@@ -42525,16 +42525,16 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-3.18979299296628</v>
+        <v>-3.247522251691863</v>
       </c>
       <c r="E1783" t="n">
-        <v>1.809414479576441</v>
+        <v>1.786322776086207</v>
       </c>
       <c r="F1783" t="n">
-        <v>0.2757252969023769</v>
+        <v>0.2179960381767936</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.251123279218127</v>
+        <v>3.216485723982777</v>
       </c>
     </row>
     <row r="1784">
@@ -42548,16 +42548,16 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-3.201598343284913</v>
+        <v>-3.259327602010496</v>
       </c>
       <c r="E1784" t="n">
-        <v>1.80870842820853</v>
+        <v>1.785616724718297</v>
       </c>
       <c r="F1784" t="n">
-        <v>0.2639199465837443</v>
+        <v>0.206190687858161</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.24805615778649</v>
+        <v>3.21341860255114</v>
       </c>
     </row>
     <row r="1785">
@@ -42571,16 +42571,16 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-3.192866532506247</v>
+        <v>-3.25059579123183</v>
       </c>
       <c r="E1785" t="n">
-        <v>1.818148610129886</v>
+        <v>1.795056906639653</v>
       </c>
       <c r="F1785" t="n">
-        <v>0.2726517573624105</v>
+        <v>0.2149224986368273</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.25924270186358</v>
+        <v>3.22460514662823</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-3.186529645861794</v>
+        <v>-3.244258904587378</v>
       </c>
       <c r="E1786" t="n">
-        <v>1.815994183735652</v>
+        <v>1.792902480245419</v>
       </c>
       <c r="F1786" t="n">
-        <v>0.2726517573624105</v>
+        <v>0.2149224986368273</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.254553520811565</v>
+        <v>3.219915965576215</v>
       </c>
     </row>
     <row r="1787">
@@ -42617,16 +42617,16 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-3.183995198134426</v>
+        <v>-3.241724456860009</v>
       </c>
       <c r="E1787" t="n">
-        <v>1.826970620628793</v>
+        <v>1.80387891713856</v>
       </c>
       <c r="F1787" t="n">
-        <v>0.2726517573624105</v>
+        <v>0.2149224986368273</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.264516178613759</v>
+        <v>3.229878623378409</v>
       </c>
     </row>
     <row r="1788">
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-3.184071097115031</v>
+        <v>-3.241800355840614</v>
       </c>
       <c r="E1788" t="n">
-        <v>1.819354941229461</v>
+        <v>1.796263237739228</v>
       </c>
       <c r="F1788" t="n">
-        <v>0.2734150180517374</v>
+        <v>0.2156857593261541</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.257388815220264</v>
+        <v>3.222751259984915</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-3.194573286674377</v>
+        <v>-3.252302545399961</v>
       </c>
       <c r="E1789" t="n">
-        <v>1.792918641196096</v>
+        <v>1.769826937705863</v>
       </c>
       <c r="F1789" t="n">
-        <v>0.2629128284923908</v>
+        <v>0.2051835697668075</v>
       </c>
       <c r="G1789" t="n">
-        <v>3.22885207727503</v>
+        <v>3.19421452203968</v>
       </c>
     </row>
     <row r="1790">
@@ -42686,16 +42686,16 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-3.196406549353493</v>
+        <v>-3.254135808079077</v>
       </c>
       <c r="E1790" t="n">
-        <v>1.792886175970571</v>
+        <v>1.769794472480338</v>
       </c>
       <c r="F1790" t="n">
-        <v>0.2629128284923908</v>
+        <v>0.2051835697668075</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.229552917121151</v>
+        <v>3.194915361885802</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-3.201415664415078</v>
+        <v>-3.259144923140661</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.791399609774797</v>
+        <v>1.768307906284563</v>
       </c>
       <c r="F1791" t="n">
-        <v>0.2619182509338561</v>
+        <v>0.2041889922082728</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.22947325041489</v>
+        <v>3.19483569517954</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-3.205121221051892</v>
+        <v>-3.262850479777475</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.789145112360436</v>
+        <v>1.766053408870203</v>
       </c>
       <c r="F1792" t="n">
-        <v>0.2600485756762211</v>
+        <v>0.2023193169506379</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.227579170500674</v>
+        <v>3.192941615265325</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-3.203888895694527</v>
+        <v>-3.26161815442011</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.790057894565702</v>
+        <v>1.766966191075469</v>
       </c>
       <c r="F1793" t="n">
-        <v>0.2606789520482587</v>
+        <v>0.2029496933226754</v>
       </c>
       <c r="G1793" t="n">
-        <v>3.228377248386217</v>
+        <v>3.193739693150866</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-3.193560898678674</v>
+        <v>-3.251290157404258</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.798319001536256</v>
+        <v>1.775227298046023</v>
       </c>
       <c r="F1794" t="n">
-        <v>0.2710069490641109</v>
+        <v>0.2132776903385276</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.238703954759941</v>
+        <v>3.204066399524591</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-3.193444563531119</v>
+        <v>-3.251173822256702</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.804886195797115</v>
+        <v>1.781794492306882</v>
       </c>
       <c r="F1795" t="n">
-        <v>0.2711232842116666</v>
+        <v>0.2133940254860833</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.245294416050311</v>
+        <v>3.210656860814961</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-3.195289973107986</v>
+        <v>-3.253019231833569</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.801122002411757</v>
+        <v>1.778030298921523</v>
       </c>
       <c r="F1796" t="n">
-        <v>0.2711232842116666</v>
+        <v>0.2133940254860833</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.2422683864957</v>
+        <v>3.207630831260349</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-3.193791540582887</v>
+        <v>-3.25152079930847</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.80165966328293</v>
+        <v>1.778567959792696</v>
       </c>
       <c r="F1797" t="n">
-        <v>0.2726217167367655</v>
+        <v>0.2148924580111822</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.243105733871892</v>
+        <v>3.208468178636542</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-3.201855792775621</v>
+        <v>-3.259585051501204</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.799711940349148</v>
+        <v>1.776620236858914</v>
       </c>
       <c r="F1798" t="n">
-        <v>0.2645574645440317</v>
+        <v>0.2068282058184484</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.239545160499564</v>
+        <v>3.204907605264214</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-3.203185760236833</v>
+        <v>-3.260915018962416</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.799179953364663</v>
+        <v>1.776088249874429</v>
       </c>
       <c r="F1799" t="n">
-        <v>0.2645574645440317</v>
+        <v>0.2068282058184484</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.239545160499564</v>
+        <v>3.204907605264214</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-2.975321077503322</v>
+        <v>-3.033050336228905</v>
       </c>
       <c r="E1800" t="n">
-        <v>1.892542299565229</v>
+        <v>1.869450596074996</v>
       </c>
       <c r="F1800" t="n">
-        <v>0.2645574645440317</v>
+        <v>0.2068282058184484</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.241761633606726</v>
+        <v>3.207124078371376</v>
       </c>
     </row>
     <row r="1801">
@@ -42939,16 +42939,16 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-2.727219513636105</v>
+        <v>-2.784948772361688</v>
       </c>
       <c r="E1801" t="n">
-        <v>1.999317521457208</v>
+        <v>1.976225817966975</v>
       </c>
       <c r="F1801" t="n">
-        <v>0.2645574645440317</v>
+        <v>0.2068282058184484</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.249296229951818</v>
+        <v>3.214658674716468</v>
       </c>
     </row>
     <row r="1802">
@@ -42962,16 +42962,16 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-2.430381114242775</v>
+        <v>-2.488110372968358</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.119475892187998</v>
+        <v>2.096384188697765</v>
       </c>
       <c r="F1802" t="n">
-        <v>0.3794119530251593</v>
+        <v>0.3216826942995761</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.319631934013952</v>
+        <v>3.284994378778602</v>
       </c>
     </row>
     <row r="1803">
@@ -42985,16 +42985,16 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-2.126741557417339</v>
+        <v>-2.184470816142922</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.242608789383859</v>
+        <v>2.219517085893626</v>
       </c>
       <c r="F1803" t="n">
-        <v>0.3794119530251593</v>
+        <v>0.3216826942995761</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.321309008479639</v>
+        <v>3.286671453244288</v>
       </c>
     </row>
     <row r="1804">
@@ -43008,16 +43008,16 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-1.83772095097663</v>
+        <v>-1.895450209702213</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.3541564534096</v>
+        <v>2.331064749919367</v>
       </c>
       <c r="F1804" t="n">
-        <v>0.3794119530251593</v>
+        <v>0.3216826942995761</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.317248429929096</v>
+        <v>3.282610874693746</v>
       </c>
     </row>
     <row r="1805">
@@ -43031,16 +43031,16 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-1.553001023712733</v>
+        <v>-1.610730282438316</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.473264563659177</v>
+        <v>2.450172860168943</v>
       </c>
       <c r="F1805" t="n">
-        <v>0.6641318802890566</v>
+        <v>0.6064026215634732</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.493300525631452</v>
+        <v>3.458662970396102</v>
       </c>
     </row>
     <row r="1806">
@@ -43054,16 +43054,16 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-1.269239354221192</v>
+        <v>-1.326968612946776</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.5920813946296</v>
+        <v>2.568989691139366</v>
       </c>
       <c r="F1806" t="n">
-        <v>0.6641318802890566</v>
+        <v>0.6064026215634732</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.498612688805259</v>
+        <v>3.463975133569909</v>
       </c>
     </row>
     <row r="1807">
@@ -43077,16 +43077,16 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-1.007590959828552</v>
+        <v>-1.065320218554135</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.689983339833289</v>
+        <v>2.666891636343056</v>
       </c>
       <c r="F1807" t="n">
-        <v>0.9257802746816972</v>
+        <v>0.8680510159561139</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.648844312887477</v>
+        <v>3.614206757652127</v>
       </c>
     </row>
     <row r="1808">
@@ -43100,16 +43100,16 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-0.6934245216892193</v>
+        <v>-0.7511537804148026</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.813113590105135</v>
+        <v>2.790021886614901</v>
       </c>
       <c r="F1808" t="n">
-        <v>1.23994671282103</v>
+        <v>1.182217454095446</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.834807850787189</v>
+        <v>3.800170295551839</v>
       </c>
     </row>
     <row r="1809">
@@ -43123,16 +43123,16 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-0.5709128175834469</v>
+        <v>-0.6286420763090302</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.880532655374183</v>
+        <v>2.857440951883949</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.362458416926802</v>
+        <v>1.304729158201219</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.926729256877391</v>
+        <v>3.892091701642041</v>
       </c>
     </row>
     <row r="1810">
@@ -43146,16 +43146,16 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-0.4095242836567186</v>
+        <v>-0.4672535423823019</v>
       </c>
       <c r="E1810" t="n">
-        <v>2.954904193000353</v>
+        <v>2.931812489510119</v>
       </c>
       <c r="F1810" t="n">
-        <v>1.52384695085353</v>
+        <v>1.466117692127947</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.033378501288907</v>
+        <v>3.998740946053557</v>
       </c>
     </row>
     <row r="1811">
@@ -43169,16 +43169,16 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>-0.2297780925082124</v>
+        <v>-0.2875073512337957</v>
       </c>
       <c r="E1811" t="n">
-        <v>3.040330281511687</v>
+        <v>3.017238578021454</v>
       </c>
       <c r="F1811" t="n">
-        <v>1.52384695085353</v>
+        <v>1.466117692127947</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.046906113340839</v>
+        <v>4.012268558105489</v>
       </c>
     </row>
     <row r="1812">
@@ -43192,16 +43192,16 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>-0.07097716603698945</v>
+        <v>-0.1287064247625728</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.110438032351442</v>
+        <v>3.087346328861209</v>
       </c>
       <c r="F1812" t="n">
-        <v>1.52384695085353</v>
+        <v>1.466117692127947</v>
       </c>
       <c r="G1812" t="n">
-        <v>4.053493493592105</v>
+        <v>4.018855938356754</v>
       </c>
     </row>
     <row r="1813">
@@ -43215,16 +43215,16 @@
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>0.02181129226838741</v>
+        <v>-0.03591796645719592</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.136464164108299</v>
+        <v>3.113372460618066</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.616635409158907</v>
+        <v>1.558906150433324</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.098077317010037</v>
+        <v>4.063439761774687</v>
       </c>
     </row>
     <row r="1814">
@@ -43238,16 +43238,16 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>0.1158317876392293</v>
+        <v>0.05810252891364598</v>
       </c>
       <c r="E1814" t="n">
-        <v>3.16967285976736</v>
+        <v>3.146581156277127</v>
       </c>
       <c r="F1814" t="n">
-        <v>1.626477849651891</v>
+        <v>1.568748590926307</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.099583278816551</v>
+        <v>4.064945723581201</v>
       </c>
     </row>
     <row r="1815">
@@ -43261,16 +43261,16 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>0.2059347555457524</v>
+        <v>0.148205496820169</v>
       </c>
       <c r="E1815" t="n">
-        <v>3.191693823436699</v>
+        <v>3.168602119946466</v>
       </c>
       <c r="F1815" t="n">
-        <v>1.629536043939676</v>
+        <v>1.571806785214093</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.087397971895952</v>
+        <v>4.052760416660602</v>
       </c>
     </row>
     <row r="1816">
@@ -43284,16 +43284,16 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>0.2500639262673275</v>
+        <v>0.1923346675417442</v>
       </c>
       <c r="E1816" t="n">
-        <v>3.226795070480458</v>
+        <v>3.203703366990225</v>
       </c>
       <c r="F1816" t="n">
-        <v>1.713555216926947</v>
+        <v>1.655825958201363</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.155259054443444</v>
+        <v>4.120621499208093</v>
       </c>
     </row>
     <row r="1817">
@@ -43307,16 +43307,16 @@
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>0.2598339704450223</v>
+        <v>0.202104711719439</v>
       </c>
       <c r="E1817" t="n">
-        <v>3.229731138535613</v>
+        <v>3.20663943504538</v>
       </c>
       <c r="F1817" t="n">
-        <v>1.792914107982013</v>
+        <v>1.735184849256429</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.20190243946056</v>
+        <v>4.16726488422521</v>
       </c>
     </row>
     <row r="1818">
@@ -43324,22 +43324,22 @@
         <v>45280</v>
       </c>
       <c r="B1818" t="n">
-        <v>3.12115005756498</v>
+        <v>3.146291510059739</v>
       </c>
       <c r="C1818" t="n">
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>0.2937929821228524</v>
+        <v>0.2958242051428847</v>
       </c>
       <c r="E1818" t="n">
-        <v>3.232617464289588</v>
+        <v>3.233429953497601</v>
       </c>
       <c r="F1818" t="n">
-        <v>1.792914107982013</v>
+        <v>1.735184849256429</v>
       </c>
       <c r="G1818" t="n">
-        <v>4.191205160543403</v>
+        <v>4.156567605308052</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231221.xlsx
+++ b/tame_output/ON/bt/strategyON_20231221.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-112.8%</t>
+          <t>-112.9%</t>
         </is>
       </c>
     </row>
@@ -43330,10 +43330,10 @@
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>0.2958242051428847</v>
+        <v>0.2954050984054992</v>
       </c>
       <c r="E1818" t="n">
-        <v>3.233429953497601</v>
+        <v>3.233262310802646</v>
       </c>
       <c r="F1818" t="n">
         <v>1.735184849256429</v>

--- a/tame_output/ON/bt/strategyON_20231221.xlsx
+++ b/tame_output/ON/bt/strategyON_20231221.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>465.5%</t>
+          <t>469.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-112.9%</t>
+          <t>-118.5%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-21.4%</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083877</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666734</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097099</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762259</v>
+        <v>3.169279212762258</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -43330,10 +43330,10 @@
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>0.2954050984054992</v>
+        <v>0.2387430344874137</v>
       </c>
       <c r="E1818" t="n">
-        <v>3.233262310802646</v>
+        <v>3.210597485235412</v>
       </c>
       <c r="F1818" t="n">
         <v>1.735184849256429</v>

--- a/tame_output/ON/bt/strategyON_20231221.xlsx
+++ b/tame_output/ON/bt/strategyON_20231221.xlsx
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083876</v>
+        <v>3.136752015083877</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666733</v>
+        <v>3.162269743666734</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097098</v>
+        <v>3.163432091097099</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762258</v>
+        <v>3.169279212762259</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
